--- a/parser/data/xlsx/preprocess_2.xlsx
+++ b/parser/data/xlsx/preprocess_2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T16:56:44.166288</t>
+          <t>2026-02-25T17:23:31.123334</t>
         </is>
       </c>
     </row>
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0a05cb32-2700-44d7-b6c8-e69700564f6f</t>
+          <t>393be70b-2760-4402-b968-a900df46a52e</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_c24603f2.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_0b0ba787.csv</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_c24603f2_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_0b0ba787_final.csv</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>threshold=0.95, dropped_columns=international_plan_0.6931471805599453, total_eve_charge, total_day_minutes, voice_mail_plan_0.0, voice_mail_plan_0.6931471805599453, total_intl_charge, total_night_charge</t>
+          <t>threshold=0.95, dropped_columns=total_intl_charge, international_plan_0.6931471805599453, total_eve_charge, voice_mail_plan_0.6931471805599453, total_night_charge, total_day_minutes, voice_mail_plan_0.0</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/preprocess_2.xlsx
+++ b/parser/data/xlsx/preprocess_2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T17:23:31.123334</t>
+          <t>2026-02-25T18:04:20.145865</t>
         </is>
       </c>
     </row>
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>393be70b-2760-4402-b968-a900df46a52e</t>
+          <t>d2991275-8bd1-4891-9a74-05fac8c1f674</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_0b0ba787.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_7ee3ce34.csv</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_0b0ba787_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_7ee3ce34_final.csv</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>threshold=0.95, dropped_columns=total_intl_charge, international_plan_0.6931471805599453, total_eve_charge, voice_mail_plan_0.6931471805599453, total_night_charge, total_day_minutes, voice_mail_plan_0.0</t>
+          <t>threshold=0.95, dropped_columns=international_plan_0.6931471805599453, total_day_minutes, voice_mail_plan_0.6931471805599453, voice_mail_plan_0.0, total_night_charge, total_eve_charge, total_intl_charge</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/preprocess_2.xlsx
+++ b/parser/data/xlsx/preprocess_2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T18:04:20.145865</t>
+          <t>2026-02-26T13:48:51.725080</t>
         </is>
       </c>
     </row>
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>d2991275-8bd1-4891-9a74-05fac8c1f674</t>
+          <t>0cdce9cb-7efe-4ba2-b745-2071ff6b7348</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_7ee3ce34.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_ca031a75.csv</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_7ee3ce34_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_ca031a75_final.csv</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>threshold=0.95, dropped_columns=international_plan_0.6931471805599453, total_day_minutes, voice_mail_plan_0.6931471805599453, voice_mail_plan_0.0, total_night_charge, total_eve_charge, total_intl_charge</t>
+          <t>threshold=0.95, dropped_columns=total_day_minutes, international_plan_0.6931471805599453, voice_mail_plan_0.6931471805599453, total_intl_charge, total_night_charge, voice_mail_plan_0.0, total_eve_charge</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/preprocess_2.xlsx
+++ b/parser/data/xlsx/preprocess_2.xlsx
@@ -418,7 +418,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="109" customWidth="1" min="2" max="2"/>
+    <col width="137" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-26T13:48:51.725080</t>
+          <t>2026-02-26T14:46:12.041014</t>
         </is>
       </c>
     </row>
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0cdce9cb-7efe-4ba2-b745-2071ff6b7348</t>
+          <t>bb008549-d3df-465d-acd7-b232b9420c64</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_ca031a75.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348.csv</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_ca031a75_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final.csv</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>threshold=0.95, dropped_columns=total_day_minutes, international_plan_0.6931471805599453, voice_mail_plan_0.6931471805599453, total_intl_charge, total_night_charge, voice_mail_plan_0.0, total_eve_charge</t>
+          <t>threshold=0.95, dropped_columns=total_day_minutes, total_night_charge, total_intl_charge, total_eve_charge, voice_mail_plan_0.6931471805599453, voice_mail_plan_0.0, international_plan_0.6931471805599453</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/preprocess_2.xlsx
+++ b/parser/data/xlsx/preprocess_2.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-26T14:46:12.041014</t>
+          <t>2026-02-26T14:55:26.285260</t>
         </is>
       </c>
     </row>
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bb008549-d3df-465d-acd7-b232b9420c64</t>
+          <t>3c8d9aba-e747-404c-93ba-1598590ce4e9</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4.csv</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final.csv</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/preprocess_2.xlsx
+++ b/parser/data/xlsx/preprocess_2.xlsx
@@ -9,6 +9,10 @@
   <sheets>
     <sheet name="record_1_metadata" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="record_1_strategy_logs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="record_2_metadata" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="record_2_strategy_logs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="record_3_metadata" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="record_3_strategy_logs" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -602,4 +606,404 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="109" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-02-27T14:08:48.035419</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>experiment_id</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0c3f70a1-2e88-42a5-93b3-798bdc09e68d</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>source_preprocessed_file</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_c13340b5.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>final_dataset</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_c13340b5_final.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>primary_model</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>kmeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>problem_type</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>unsupervised</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>columns</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="308" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>data_sanity</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dropped_columns=Unnamed: 28, accident</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>onehot_columns=belts, personal_injury, property_damage, fatal, commercial_license, hazmat, commercial_vehicle, alcohol, work_zone, vehicletype, color, violation_type, contributed_to_accident, race, gender, frequency_columns=description, location, make, model, driver_state, dl_state, final_columns_added=21</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>scaling</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>scaled_columns=latitude, longitude, year</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>correlation_resolution</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>threshold=0.95, dropped_columns=commercial_license_Yes, contributed_to_accident_Yes, commercial_vehicle_Yes, work_zone_Yes, personal_injury_No, gender_F, alcohol_Yes, hazmat_Yes, belts_Yes, fatal_No, property_damage_Yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="137" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-02-27T14:13:21.962976</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>experiment_id</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c3f5ac6e-72a6-4cfb-b346-80fda5315782</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>source_preprocessed_file</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\42d1e5bfc1a9434c8980fd2b57f3f8d8_preprocessed_1_40ded763.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>final_dataset</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\42d1e5bfc1a9434c8980fd2b57f3f8d8_preprocessed_1_40ded763_final.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>primary_model</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>kmeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>problem_type</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>unsupervised</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>columns</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="308" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>data_sanity</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dropped_columns=accident, Unnamed: 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>onehot_columns=belts, personal_injury, property_damage, fatal, commercial_license, hazmat, commercial_vehicle, alcohol, work_zone, vehicletype, color, violation_type, contributed_to_accident, race, gender, frequency_columns=description, location, make, model, driver_state, dl_state, final_columns_added=21</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>scaling</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>scaled_columns=latitude, longitude, year</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>correlation_resolution</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>threshold=0.95, dropped_columns=property_damage_Yes, belts_Yes, fatal_No, alcohol_Yes, commercial_vehicle_Yes, hazmat_Yes, personal_injury_No, gender_F, commercial_license_Yes, contributed_to_accident_Yes, work_zone_Yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>